--- a/AAII_Financials/Yearly/CRC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRC_YR_FIN.xlsx
@@ -786,7 +786,7 @@
         <v>1551000</v>
       </c>
       <c r="E9" s="3">
-        <v>1294000</v>
+        <v>1293000</v>
       </c>
       <c r="F9" s="3">
         <v>1216000</v>
@@ -837,7 +837,7 @@
         <v>1852000</v>
       </c>
       <c r="E10" s="3">
-        <v>1663000</v>
+        <v>1664000</v>
       </c>
       <c r="F10" s="3">
         <v>1597000</v>
@@ -1008,10 +1008,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>139000</v>
+        <v>82000</v>
       </c>
       <c r="E14" s="3">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="F14" s="3">
         <v>-28000</v>
@@ -1059,7 +1059,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>511000</v>
+        <v>568000</v>
       </c>
       <c r="E15" s="3">
         <v>388000</v>
@@ -1128,10 +1128,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2656000</v>
+        <v>2713000</v>
       </c>
       <c r="E17" s="3">
-        <v>2240000</v>
+        <v>2239000</v>
       </c>
       <c r="F17" s="3">
         <v>2025000</v>
@@ -1179,10 +1179,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>747000</v>
+        <v>690000</v>
       </c>
       <c r="E18" s="3">
-        <v>717000</v>
+        <v>718000</v>
       </c>
       <c r="F18" s="3">
         <v>788000</v>
@@ -1305,7 +1305,7 @@
         <v>1258000</v>
       </c>
       <c r="E21" s="3">
-        <v>1090000</v>
+        <v>1091000</v>
       </c>
       <c r="F21" s="3">
         <v>1001000</v>
